--- a/1. Reporting_Data/IB_Mark-to-Market PnL/AssetCurrency/2026/202608/Currency_P&L_20260805.xlsx
+++ b/1. Reporting_Data/IB_Mark-to-Market PnL/AssetCurrency/2026/202608/Currency_P&L_20260805.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Date</t>
   </si>
@@ -44,6 +44,24 @@
   </si>
   <si>
     <t>United States Return</t>
+  </si>
+  <si>
+    <t>United Kingdom MTM</t>
+  </si>
+  <si>
+    <t>United Kingdom Return</t>
+  </si>
+  <si>
+    <t>South Korea MTM</t>
+  </si>
+  <si>
+    <t>South Korea Return</t>
+  </si>
+  <si>
+    <t>Taiwan MTM</t>
+  </si>
+  <si>
+    <t>Taiwan Return</t>
   </si>
 </sst>
 </file>
@@ -405,10 +423,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:P45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -439,8 +457,26 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" s="2">
         <v>46176</v>
       </c>
@@ -472,7 +508,7 @@
         <v>-0.002062</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:16">
       <c r="A3" s="2">
         <v>46177</v>
       </c>
@@ -504,7 +540,7 @@
         <v>-0.01325</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:16">
       <c r="A4" s="2">
         <v>46178</v>
       </c>
@@ -536,7 +572,7 @@
         <v>-0.057191</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:16">
       <c r="A5" s="2">
         <v>46181</v>
       </c>
@@ -568,7 +604,7 @@
         <v>0.013874</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:16">
       <c r="A6" s="2">
         <v>46182</v>
       </c>
@@ -600,7 +636,7 @@
         <v>-0.00732</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:16">
       <c r="A7" s="2">
         <v>46183</v>
       </c>
@@ -632,7 +668,7 @@
         <v>-0.013745</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:16">
       <c r="A8" s="2">
         <v>46184</v>
       </c>
@@ -664,7 +700,7 @@
         <v>0.027766</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:16">
       <c r="A9" s="2">
         <v>46185</v>
       </c>
@@ -696,7 +732,7 @@
         <v>0.001551</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:16">
       <c r="A10" s="2">
         <v>46188</v>
       </c>
@@ -728,7 +764,7 @@
         <v>0.015633</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:16">
       <c r="A11" s="2">
         <v>46189</v>
       </c>
@@ -760,7 +796,7 @@
         <v>-0.009766</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:16">
       <c r="A12" s="2">
         <v>46190</v>
       </c>
@@ -792,7 +828,7 @@
         <v>-0.00462</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:16">
       <c r="A13" s="2">
         <v>46191</v>
       </c>
@@ -824,7 +860,7 @@
         <v>0.002327</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:16">
       <c r="A14" s="2">
         <v>46195</v>
       </c>
@@ -856,7 +892,7 @@
         <v>-0.000175</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:16">
       <c r="A15" s="2">
         <v>46196</v>
       </c>
@@ -888,7 +924,7 @@
         <v>-0.020594</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:16">
       <c r="A16" s="2">
         <v>46197</v>
       </c>
@@ -1432,7 +1468,7 @@
         <v>-0.017473</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:16">
       <c r="A33" s="2">
         <v>46223</v>
       </c>
@@ -1464,7 +1500,7 @@
         <v>0.001085</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:16">
       <c r="A34" s="2">
         <v>46224</v>
       </c>
@@ -1496,7 +1532,7 @@
         <v>0.034142</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:16">
       <c r="A35" s="2">
         <v>46225</v>
       </c>
@@ -1528,7 +1564,7 @@
         <v>-0.000831</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:16">
       <c r="A36" s="2">
         <v>46226</v>
       </c>
@@ -1560,7 +1596,7 @@
         <v>-0.009573999999999999</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:16">
       <c r="A37" s="2">
         <v>46227</v>
       </c>
@@ -1592,7 +1628,7 @@
         <v>-0.013868</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:16">
       <c r="A38" s="2">
         <v>46230</v>
       </c>
@@ -1624,7 +1660,7 @@
         <v>-0.007622</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:16">
       <c r="A39" s="2">
         <v>46231</v>
       </c>
@@ -1656,7 +1692,7 @@
         <v>-0.014188</v>
       </c>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:16">
       <c r="A40" s="2">
         <v>46232</v>
       </c>
@@ -1688,12 +1724,12 @@
         <v>-0.021684</v>
       </c>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:16">
       <c r="A41" s="2">
         <v>46233</v>
       </c>
       <c r="B41">
-        <v>85859219.67</v>
+        <v>87859219.67</v>
       </c>
       <c r="C41">
         <v>30846.08</v>
@@ -1720,132 +1756,180 @@
         <v>0.029989</v>
       </c>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:16">
       <c r="A42" s="2">
         <v>46234</v>
       </c>
       <c r="B42">
-        <v>86263492.97</v>
+        <v>88263665.98999999</v>
       </c>
       <c r="C42">
         <v>-19784.59</v>
       </c>
       <c r="D42">
-        <v>-0.00023</v>
+        <v>-0.000225</v>
       </c>
       <c r="E42">
         <v>68001.59</v>
       </c>
       <c r="F42">
-        <v>0.000792</v>
+        <v>0.0007739999999999999</v>
       </c>
       <c r="G42">
         <v>-63561.88</v>
       </c>
       <c r="H42">
-        <v>-0.00074</v>
+        <v>-0.000723</v>
       </c>
       <c r="I42">
         <v>434413.15</v>
       </c>
       <c r="J42">
-        <v>0.00506</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10">
+        <v>0.004944</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
       <c r="A43" s="2">
         <v>46237</v>
       </c>
       <c r="B43">
-        <v>87113767.19</v>
+        <v>89113874.08</v>
       </c>
       <c r="C43">
-        <v>223.1</v>
+        <v>-1413.2</v>
       </c>
       <c r="D43">
-        <v>3E-06</v>
+        <v>-1.6E-05</v>
       </c>
       <c r="E43">
         <v>-42459.98</v>
       </c>
       <c r="F43">
-        <v>-0.000492</v>
+        <v>-0.000481</v>
       </c>
       <c r="G43">
-        <v>-44160.69</v>
+        <v>-45582.27</v>
       </c>
       <c r="H43">
-        <v>-0.000512</v>
+        <v>-0.000516</v>
       </c>
       <c r="I43">
-        <v>897212.4300000001</v>
+        <v>897264.64</v>
       </c>
       <c r="J43">
-        <v>0.010401</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10">
+        <v>0.010166</v>
+      </c>
+      <c r="K43">
+        <v>19.3</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>2401.18</v>
+      </c>
+      <c r="N43">
+        <v>2.7E-05</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
       <c r="A44" s="2">
         <v>46238</v>
       </c>
       <c r="B44">
-        <v>91262886.70999999</v>
+        <v>93267004.43000001</v>
       </c>
       <c r="C44">
-        <v>-36054.21</v>
+        <v>-49988.29</v>
       </c>
       <c r="D44">
-        <v>-0.000414</v>
+        <v>-0.000561</v>
       </c>
       <c r="E44">
         <v>15569.32</v>
       </c>
       <c r="F44">
-        <v>0.000179</v>
+        <v>0.000175</v>
       </c>
       <c r="G44">
-        <v>38138.16</v>
+        <v>37596.13</v>
       </c>
       <c r="H44">
-        <v>0.000438</v>
+        <v>0.000422</v>
       </c>
       <c r="I44">
-        <v>4150722.13</v>
+        <v>4149005.76</v>
       </c>
       <c r="J44">
-        <v>0.047647</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10">
+        <v>0.046558</v>
+      </c>
+      <c r="K44">
+        <v>-29.38</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>23429.3</v>
+      </c>
+      <c r="N44">
+        <v>0.000263</v>
+      </c>
+      <c r="O44">
+        <v>-3568.85</v>
+      </c>
+      <c r="P44">
+        <v>-4E-05</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
       <c r="A45" s="2">
         <v>46239</v>
       </c>
       <c r="B45">
-        <v>90306025.06999999</v>
+        <v>92301723.41</v>
       </c>
       <c r="C45">
-        <v>25387</v>
+        <v>21264.82</v>
       </c>
       <c r="D45">
-        <v>0.000278</v>
+        <v>0.000228</v>
       </c>
       <c r="E45">
-        <v>86138.85000000001</v>
+        <v>88335.56</v>
       </c>
       <c r="F45">
-        <v>0.000944</v>
+        <v>0.000947</v>
       </c>
       <c r="G45">
-        <v>-39467.47</v>
+        <v>-41322.82</v>
       </c>
       <c r="H45">
-        <v>-0.000432</v>
+        <v>-0.000443</v>
       </c>
       <c r="I45">
-        <v>-1008525.76</v>
+        <v>-1012562.54</v>
       </c>
       <c r="J45">
-        <v>-0.011051</v>
+        <v>-0.010857</v>
+      </c>
+      <c r="K45">
+        <v>-14.36</v>
+      </c>
+      <c r="L45">
+        <v>-0</v>
+      </c>
+      <c r="M45">
+        <v>-471.78</v>
+      </c>
+      <c r="N45">
+        <v>-5E-06</v>
+      </c>
+      <c r="O45">
+        <v>-241.2</v>
+      </c>
+      <c r="P45">
+        <v>-3E-06</v>
       </c>
     </row>
   </sheetData>
